--- a/Python/dz2/work/output/statistics.xlsx
+++ b/Python/dz2/work/output/statistics.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
   <si>
     <t>attribute</t>
   </si>
@@ -67,10 +67,16 @@
     <t>В приюте</t>
   </si>
   <si>
+    <t>Готов к пристройству</t>
+  </si>
+  <si>
     <t>На лечении</t>
   </si>
   <si>
     <t>Пристроено</t>
+  </si>
+  <si>
+    <t>Карантин</t>
   </si>
   <si>
     <t>F</t>
@@ -434,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -474,10 +480,10 @@
         <v>14</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D2">
-        <v>66.67</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -488,10 +494,10 @@
         <v>15</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D3">
-        <v>33.33</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -502,10 +508,10 @@
         <v>16</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D4">
-        <v>33.33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -516,10 +522,10 @@
         <v>17</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D5">
-        <v>33.33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -530,90 +536,118 @@
         <v>18</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D6">
-        <v>33.33</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>19</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D7">
-        <v>66.67</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>20</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D8">
-        <v>33.33</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D9">
-        <v>100</v>
-      </c>
-      <c r="E9">
-        <v>2.8</v>
-      </c>
-      <c r="F9">
-        <v>5.1</v>
-      </c>
-      <c r="G9">
-        <v>3.97</v>
-      </c>
-      <c r="H9">
-        <v>1.32</v>
-      </c>
-      <c r="I9">
-        <v>1.15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10">
+        <v>20</v>
+      </c>
+      <c r="D10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11">
+        <v>40</v>
+      </c>
+      <c r="D11">
+        <v>100</v>
+      </c>
+      <c r="E11">
+        <v>1.7</v>
+      </c>
+      <c r="F11">
+        <v>8</v>
+      </c>
+      <c r="G11">
+        <v>4.47</v>
+      </c>
+      <c r="H11">
+        <v>2.83</v>
+      </c>
+      <c r="I11">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
         <v>13</v>
       </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="D10">
+      <c r="C12">
+        <v>40</v>
+      </c>
+      <c r="D12">
         <v>100</v>
       </c>
-      <c r="E10">
-        <v>99</v>
-      </c>
-      <c r="F10">
-        <v>142</v>
-      </c>
-      <c r="G10">
-        <v>120</v>
-      </c>
-      <c r="H10">
-        <v>463</v>
-      </c>
-      <c r="I10">
-        <v>21.52</v>
+      <c r="E12">
+        <v>21</v>
+      </c>
+      <c r="F12">
+        <v>144</v>
+      </c>
+      <c r="G12">
+        <v>77.62</v>
+      </c>
+      <c r="H12">
+        <v>1166.91</v>
+      </c>
+      <c r="I12">
+        <v>34.16</v>
       </c>
     </row>
   </sheetData>
